--- a/jun-caifang/admin/output/俊才坊行政系統.xlsx
+++ b/jun-caifang/admin/output/俊才坊行政系統.xlsx
@@ -673,7 +673,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>v3 · 即時 KPI 連動各表總數</t>
+          <t>所有工作表關鍵總數 · 自動連動更新</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp 訊息自動生成 · 底部總數</t>
+          <t>所有工作表關鍵總數 · 自動連動更新</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>完成率自動計算 · 底部任務總數</t>
+          <t>所有工作表關鍵總數 · 自動連動更新</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>優先級 · 逾期提醒 · 底部總數</t>
+          <t>所有工作表關鍵總數 · 自動連動更新</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>學生數 · 合約倒數 · 底部薪酬總數</t>
+          <t>所有工作表關鍵總數 · 自動連動更新</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Upgrade Edition v3.0 · 各表自動計算總數</t>
+          <t>所有工作表關鍵總數 · 自動連動更新</t>
         </is>
       </c>
     </row>
@@ -4303,7 +4303,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>★ 接手首週必完成 · 底部自動計算總數</t>
+          <t>所有工作表關鍵總數 · 自動連動更新</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>自動計算差額 · 底部總數統計</t>
+          <t>所有工作表關鍵總數 · 自動連動更新</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5821,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>每日點名 · 底部出席總數統計</t>
+          <t>所有工作表關鍵總數 · 自動連動更新</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>滿班率 · 預估營收 · 底部總數</t>
+          <t>所有工作表關鍵總數 · 自動連動更新</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>空閒時段統計 · 每呎產值總數</t>
+          <t>所有工作表關鍵總數 · 自動連動更新</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>自動 P&amp;L · 底部年度總數</t>
+          <t>所有工作表關鍵總數 · 自動連動更新</t>
         </is>
       </c>
     </row>
